--- a/导入参考表格.xlsx
+++ b/导入参考表格.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="21870" windowHeight="10800" activeTab="1"/>
+    <workbookView windowWidth="21870" windowHeight="7140"/>
   </bookViews>
   <sheets>
     <sheet name="座位表" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
     <t>学生04</t>
   </si>
   <si>
-    <t>学生05(组长)</t>
+    <t>学生05（组长）</t>
   </si>
   <si>
     <t>学生06</t>
@@ -66,7 +66,7 @@
     <t>学生09</t>
   </si>
   <si>
-    <t>学生10(组长)</t>
+    <t>学生10（组长）</t>
   </si>
   <si>
     <t>学生11</t>
@@ -129,10 +129,10 @@
     <t>学生30</t>
   </si>
   <si>
-    <t>学生31(班长)</t>
-  </si>
-  <si>
-    <t>学生32(组长)</t>
+    <t>学生31（班长）</t>
+  </si>
+  <si>
+    <t>学生32（组长）</t>
   </si>
   <si>
     <t>学生33</t>
@@ -156,7 +156,7 @@
     <t>学生39</t>
   </si>
   <si>
-    <t>学生40(组长)</t>
+    <t>学生40（组长）</t>
   </si>
   <si>
     <t>学生41</t>
@@ -165,7 +165,7 @@
     <t>学生42</t>
   </si>
   <si>
-    <t>学生43(组长)</t>
+    <t>学生43（组长）</t>
   </si>
   <si>
     <t>学生44</t>
@@ -177,7 +177,7 @@
     <t>学生46</t>
   </si>
   <si>
-    <t>学生47(班长)</t>
+    <t>学生47（班长）</t>
   </si>
   <si>
     <t>学生48</t>
@@ -213,7 +213,7 @@
     <t>学生58</t>
   </si>
   <si>
-    <t>学生59(组长)</t>
+    <t>学生59（组长）</t>
   </si>
   <si>
     <t>学生60</t>
@@ -240,7 +240,7 @@
     <t>学生67</t>
   </si>
   <si>
-    <t>学生68(组长)</t>
+    <t>学生68（组长）</t>
   </si>
   <si>
     <t>学生69</t>
@@ -249,7 +249,7 @@
     <t>学生70</t>
   </si>
   <si>
-    <t>学生71(组长)</t>
+    <t>学生71（组长）</t>
   </si>
   <si>
     <t>学生72</t>
@@ -1344,6 +1344,10 @@
   <sheetPr/>
   <dimension ref="A1:Q9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="4" max="4" width="13.75" customWidth="1"/>
+    <col min="5" max="5" width="13.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
@@ -1799,7 +1803,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:Q9" numberStoredAsText="1"/>
+    <ignoredError sqref="A9:Q9 C8:Q8 A8 O7:Q7 E7:M7 A7:C7 F6:Q6 A6:D6 Q5 N5:O5 E5:L5 A5:B5 A4:Q4 L3:Q3 G3:J3 A3:E3 A1:Q2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/导入参考表格.xlsx
+++ b/导入参考表格.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="21870" windowHeight="7140"/>
+    <workbookView windowWidth="21870" windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="座位表" sheetId="1" r:id="rId1"/>
-    <sheet name="姓名典故" sheetId="2" r:id="rId2"/>
+    <sheet name="学生介绍" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -294,7 +294,7 @@
     <t>姓名</t>
   </si>
   <si>
-    <t>典故/介绍</t>
+    <t>介绍/典故/备注信息</t>
   </si>
   <si>
     <t>唐宋四大家之一</t>
@@ -2486,7 +2486,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:B83" numberStoredAsText="1"/>
+    <ignoredError sqref="A2:B83 A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>